--- a/originales/respuestas/2025/01. Calificadas/bucle p14/Agencia Analítica De Datos.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/bucle p14/Agencia Analítica De Datos.xlsx
@@ -209,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -224,6 +224,9 @@
     </xf>
     <xf borderId="4" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -524,32 +527,32 @@
       <c r="H2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="I2" s="4">
-        <v>5.0</v>
+      <c r="I2" s="5">
+        <v>2.0</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="4">
-        <v>5.0</v>
+      <c r="K2" s="5">
+        <v>2.0</v>
       </c>
       <c r="L2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="4">
-        <v>5.0</v>
+      <c r="M2" s="5">
+        <v>4.0</v>
       </c>
       <c r="N2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="O2" s="4">
-        <v>5.0</v>
+      <c r="O2" s="5">
+        <v>2.0</v>
       </c>
       <c r="P2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="Q2" s="4">
-        <v>5.0</v>
+      <c r="Q2" s="5">
+        <v>4.0</v>
       </c>
       <c r="R2" s="4"/>
     </row>
